--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/34. ЭК ВОСТОК/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/34. ЭК ВОСТОК/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92565754208</v>
+        <v>46157.93091361789</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/34. ЭК ВОСТОК/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/34. ЭК ВОСТОК/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93091361789</v>
+        <v>46157.93167843176</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/34. ЭК ВОСТОК/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/34. ЭК ВОСТОК/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93167843176</v>
+        <v>46157.93397702892</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/34. ЭК ВОСТОК/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/34. ЭК ВОСТОК/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93397702892</v>
+        <v>46157.93715450738</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/34. ЭК ВОСТОК/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/34. ЭК ВОСТОК/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93715450738</v>
+        <v>46158.28214104008</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/34. ЭК ВОСТОК/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/34. ЭК ВОСТОК/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28214104008</v>
+        <v>46158.29675469663</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/34. ЭК ВОСТОК/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/34. ЭК ВОСТОК/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29675469663</v>
+        <v>46158.29812135169</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/34. ЭК ВОСТОК/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/34. ЭК ВОСТОК/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29812135169</v>
+        <v>46158.33384977173</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/34. ЭК ВОСТОК/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/34. ЭК ВОСТОК/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33384977173</v>
+        <v>46158.36854588471</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/34. ЭК ВОСТОК/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/34. ЭК ВОСТОК/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36854588471</v>
+        <v>46158.37285216748</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
